--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,80 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>Desk Assignment</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Specialty 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Specialty 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jane Doe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>jane.doe@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support Desk</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Shipping and Delivery</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Payments and Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12346</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>john.smith@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support Desk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Shipping and Delivery</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,66 +449,4065 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jane Doe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>jane.doe@example.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Support Desk</t>
+          <t>Anastasiia Sakharuk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>12346</t>
-        </is>
-      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>john.smith@example.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Support Desk</t>
+          <t>Snizhana Zayats</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kateryna Podoliaka</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Serhii Lutsenko</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mykhailo Cherepania</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tetiana Herman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Illia Makhniuk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Solomiia Krykhivska</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anastasiia Zaika</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anastasiia Zahoruiko</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nataliia Vonitova</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sesedzai Mudzingwa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Diana Khodan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ihor Danyliak</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ashley Murerwa</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Oleksii Pavlov</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Yuliia Kravchuk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ester Kovach</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Anzhelika Kungurova</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dmytro Starozhytnyk</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nellia Kosenko</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Andrii Abramov</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dmytro Lytvynenko</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tetiana Boiko</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vladyslav Vedmid</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Oleksii Komar</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Khrystyna Vyshnivska</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anastasiia Solodka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Tsyplenko</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Karina Pilipuitis</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mariia Oros</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oleksander Sviatchenko</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Anzhela Kulakova</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bohdana Bohonos</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vladyslav Kosovskyi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Vladyslav Melnyk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tetiana Nazarenko</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Andrii Pryimenko</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tetiana Kushnir</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sofiia Maletska</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Andrii Manuliak</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nataliia Trymbaliuk</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sofiia Yukhymchuk</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ilona Havryliuk</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mariana Yuryshynets</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Anton Dmytruk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Oleksandra Horobets</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Oleksandr Feshchuk</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Vitalii Yuzvyn</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Vladyslav Koreniuk</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Karolina-Anna Sikomas</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Dmytro Skrypak</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Yuliia Matviienko</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mykola Sakalosh</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hryhorii Balychev</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bohdana Rudnevska</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Anastasiia Volkanova</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Olha Zubrytska</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Yevheniia Antonova</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Yekateryna Potsiluiko</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Andrii Venhreniuk</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Yuliia Ruban</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Niiara Abdurakhmanova</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Romanna Paniush</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Borys Suiarko</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Bohdana Kosarchyn</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kateryna Mazurenko</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Oladipo Rahmon Saliu</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Samuel Nwoke</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Anton Li</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Marina Pidkovenko</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Anton Dovhyi</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Vladyslav Melnychuk</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Olena Yaremenko1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sebastian Stroin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Olena Sharlai</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Veronika Dzhaparidze</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Nataliia Karpiuk</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sofia Hunka1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Vadym Rakitin</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Serhii Koval</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hlib Devecha</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Marta Chipko</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Korneliia Lopit</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Yuliia Udut</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Bohdan Dunaievskyi</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Yevheniia Vlasenko</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sofia Yurkiv</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ivan Bekh</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nazar-Marian Bakai</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Davyd Rozhkov</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Viktoriia Mysko</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Nazar Soloha</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Danil Diachenko</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ihor Bohdan</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Mykhailo Shcherbyna</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Anastasiia Vynnyk</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Asan Khalilov</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tetiana Krat</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Marharyta Kohut</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Yana Kovalenko</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Nadieieva</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Maksym Patrai</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Khrystyna Pelyno</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Mariia Tarasiuk</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Valentyna Vanzuriak</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Khrystyna Koprovska</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Yevhen Kushnyrik</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Maksym Kukharyk</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Danylo Hushcha</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Karolina Onyshchenko</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Yurii Sosnovskyi</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Vladyslav Tiutiunnyk</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Danyil Muravlov</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Anna Korkeshko</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Andriana Budysh</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Widgen Ropafadzo Tsabora</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Kamilla Kukri</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sviatoslav Mezhivnyk</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Daryna Stankevych</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Marta Smuk</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Volodymyr Koziupa</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Oleksii Petrov</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Mariia Popova</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Yevheniia Prokopiv</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Valentyna Bulik</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Oksana Nykoliak</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Olena Dymura</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Yevheniia Vakulina</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Kateryna Dzyha</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Roman Sivak</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Orest Labiak</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Kostiantyn Pinchuk</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Anna Pozniak</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Anna Shumyk</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Anastasiia Lavryk</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bogdan Ryabenko</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Vladyslava Zharska</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Dmytro Tkachenko</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Yelyzaveta Bozhko</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Olha Yaroshenko</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kostiantyn Pohrebniak</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Denys Lebeda</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Yuliia Zhygulina</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Diana Rudzik</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Yakiv Kysliakov</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Nazar Drahomirov</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Volodymyr Larin</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mariia Boncheva</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Maksym Orlov1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mykhailo Senychych</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Yevhen Kelembet</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Volodymyr Larin</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ihor Klimenchenko</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Maryna Polishchuk</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Anastasiia Kozbur</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Oleksandr Mykolaiko</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Valeriia Makovetska</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Olena Matviiv</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Maksym Kulish</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Victoria Kushnir</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Aleksandra Kvitka</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Mohamad Kawni</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Maryna Kibak</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Victoria Petrova</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Mykhailo Zelenchuk</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Mariia Shapovalenko</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Vladyslav Hoza</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Markiian Hanushevskyi</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Artem Sehal</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ilona Ilieva</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Makar Bytsyura</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Taras Tiurdo</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Danylo Honchar</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ivan Horobets</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Illia Yaremenko</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Anastasiia Ratushna</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Daniil Komiakov</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Denys Fedchenko</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Olesia Kuzyk</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Anastasiya Skibynska</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ivan Kravchenko</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Valerii Zaiarnyi</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Viktoriia Avramenko</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Anhelina Turianska</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Olena Halaktionova</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Vitalii Radchenko</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Petro Fenenko</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Yevhen Fedorchenko</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sofiia Zaianchkivska</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Oleksandr Matviichuk</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Valerii Toderiuk</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Mariana Humeniuk</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Viktor Lyulka</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Liudmyla Plekhanova</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Yehor Keller</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Dmytro Suprunets</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Viktor Dunets</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nikita Havryliuk</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Yuliia Bosko</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Alona Dehtiar</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Alina Nikolaieva</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Anastasiia Zykova</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Maksym Olynets</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Oleksandr Prepiialo</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Vadym Kharchenko</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Nikol Benua Berko</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Dmytro Mitsiuk</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Eduard Nesterenko</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Mariia Bodak</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Vitalii Marchenko</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Kostiantyn Bratchenko</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Romana Hrynovets</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Olha Prymak</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Veronika Bondar</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nika Karpinska</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Valeriia Sereda</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Taras Tatarskyi</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Danylo Zhurniev</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Sofiia Bilyk</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Yuliia Hlynska</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Roman Zavhorodnii</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Artem Stratonov</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Denys Pronkin</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Valerii Pylypenko</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Kateryna Lohin</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Arsen Shkolnyi</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Melusi Karen Kombore</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Kateryna Vasylovych</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Lolita Liushyn</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Alyona Zalevska</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Privacy &amp; Legal</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Iryna Tsolta</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Mykyta Koval</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sofiia Komziuk</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Dmytro Chaievskyi</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Diana Rykhalska</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Oleh Metlenko</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Maksym Starominskyi</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Payments &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Denys Hohol</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -456,12 +456,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -473,12 +473,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -507,12 +507,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -558,12 +558,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -575,12 +575,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2734,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3142,12 +3142,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3516,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3907,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3958,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4060,12 +4060,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Privacy &amp; Legal</t>
+          <t>Privacy and Legal</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Payments &amp; Safety</t>
+          <t>Payments and Safety</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
     </row>
@@ -4502,12 +4502,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Shipping &amp; Delivery</t>
+          <t>Shipping and Delivery</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Order Quality &amp; Usability</t>
+          <t>Order Quality and Usability</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -454,6 +454,11 @@
           <t>Anastasiia Sakharuk</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -471,6 +476,11 @@
           <t>Snizhana Zayats</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -488,6 +498,11 @@
           <t>Kateryna Podoliaka</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -505,6 +520,11 @@
           <t>Serhii Lutsenko</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -522,6 +542,11 @@
           <t>Mykhailo Cherepania</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -539,6 +564,11 @@
           <t>Tetiana Herman</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -556,6 +586,11 @@
           <t>Illia Makhniuk</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -573,6 +608,11 @@
           <t>Solomiia Krykhivska</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -590,6 +630,11 @@
           <t>Anastasiia Zaika</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -607,6 +652,11 @@
           <t>Anastasiia Zahoruiko</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -624,6 +674,11 @@
           <t>Nataliia Vonitova</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -641,6 +696,11 @@
           <t>Sesedzai Mudzingwa</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -658,6 +718,11 @@
           <t>Diana Khodan</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -675,6 +740,11 @@
           <t>Ihor Danyliak</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -692,6 +762,11 @@
           <t>Ashley Murerwa</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -709,6 +784,11 @@
           <t>Oleksii Pavlov</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -726,6 +806,11 @@
           <t>Yuliia Kravchuk</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -743,6 +828,11 @@
           <t>Ester Kovach</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -760,6 +850,11 @@
           <t>Anzhelika Kungurova</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -777,6 +872,11 @@
           <t>Dmytro Starozhytnyk</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -794,6 +894,11 @@
           <t>Nellia Kosenko</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -811,6 +916,11 @@
           <t>Andrii Abramov</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -828,6 +938,11 @@
           <t>Dmytro Lytvynenko</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -845,6 +960,11 @@
           <t>Tetiana Boiko</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -862,6 +982,11 @@
           <t>Vladyslav Vedmid</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -879,6 +1004,11 @@
           <t>Oleksii Komar</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -896,6 +1026,11 @@
           <t>Khrystyna Vyshnivska</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -913,6 +1048,11 @@
           <t>Anastasiia Solodka</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -930,6 +1070,11 @@
           <t>Yelyzaveta Tsyplenko</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -947,6 +1092,11 @@
           <t>Karina Pilipuitis</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -964,6 +1114,11 @@
           <t>Mariia Oros</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -981,6 +1136,11 @@
           <t>Oleksander Sviatchenko</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -998,6 +1158,11 @@
           <t>Anzhela Kulakova</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1015,6 +1180,11 @@
           <t>Bohdana Bohonos</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1032,6 +1202,11 @@
           <t>Vladyslav Kosovskyi</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1049,6 +1224,11 @@
           <t>Vladyslav Melnyk</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1066,6 +1246,11 @@
           <t>Tetiana Nazarenko</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1083,6 +1268,11 @@
           <t>Andrii Pryimenko</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1100,6 +1290,11 @@
           <t>Tetiana Kushnir</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1117,6 +1312,11 @@
           <t>Sofiia Maletska</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1134,6 +1334,11 @@
           <t>Andrii Manuliak</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1151,6 +1356,11 @@
           <t>Nataliia Trymbaliuk</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1168,6 +1378,11 @@
           <t>Sofiia Yukhymchuk</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1185,6 +1400,11 @@
           <t>Ilona Havryliuk</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1202,6 +1422,11 @@
           <t>Mariana Yuryshynets</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1219,6 +1444,11 @@
           <t>Anton Dmytruk</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1236,6 +1466,11 @@
           <t>Oleksandra Horobets</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1253,6 +1488,11 @@
           <t>Oleksandr Feshchuk</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1270,6 +1510,11 @@
           <t>Vitalii Yuzvyn</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1287,6 +1532,11 @@
           <t>Vladyslav Koreniuk</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1304,6 +1554,11 @@
           <t>Karolina-Anna Sikomas</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1321,6 +1576,11 @@
           <t>Dmytro Skrypak</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1338,6 +1598,11 @@
           <t>Yuliia Matviienko</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1355,6 +1620,11 @@
           <t>Mykola Sakalosh</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1372,6 +1642,11 @@
           <t>Hryhorii Balychev</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1389,6 +1664,11 @@
           <t>Bohdana Rudnevska</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1406,6 +1686,11 @@
           <t>Anastasiia Volkanova</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1423,6 +1708,11 @@
           <t>Olha Zubrytska</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1440,6 +1730,11 @@
           <t>Yevheniia Antonova</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1457,6 +1752,11 @@
           <t>Yekateryna Potsiluiko</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1474,6 +1774,11 @@
           <t>Andrii Venhreniuk</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -1491,6 +1796,11 @@
           <t>Yuliia Ruban</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1508,6 +1818,11 @@
           <t>Niiara Abdurakhmanova</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -1525,6 +1840,11 @@
           <t>Romanna Paniush</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -1542,6 +1862,11 @@
           <t>Borys Suiarko</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1559,6 +1884,11 @@
           <t>Bohdana Kosarchyn</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1576,6 +1906,11 @@
           <t>Kateryna Mazurenko</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1593,6 +1928,11 @@
           <t>Oladipo Rahmon Saliu</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1610,6 +1950,11 @@
           <t>Samuel Nwoke</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1627,6 +1972,11 @@
           <t>Anton Li</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1644,6 +1994,11 @@
           <t>Marina Pidkovenko</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1661,6 +2016,11 @@
           <t>Anton Dovhyi</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1678,6 +2038,11 @@
           <t>Vladyslav Melnychuk</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1695,6 +2060,11 @@
           <t>Olena Yaremenko1</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1712,6 +2082,11 @@
           <t>Sebastian Stroin</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1729,6 +2104,11 @@
           <t>Olena Sharlai</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1746,6 +2126,11 @@
           <t>Veronika Dzhaparidze</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1763,6 +2148,11 @@
           <t>Nataliia Karpiuk</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1780,6 +2170,11 @@
           <t>Sofia Hunka1</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1797,6 +2192,11 @@
           <t>Vadym Rakitin</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1814,6 +2214,11 @@
           <t>Serhii Koval</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1831,6 +2236,11 @@
           <t>Hlib Devecha</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1848,6 +2258,11 @@
           <t>Marta Chipko</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1865,6 +2280,11 @@
           <t>Korneliia Lopit</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1882,6 +2302,11 @@
           <t>Yuliia Udut</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1899,6 +2324,11 @@
           <t>Bohdan Dunaievskyi</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -1916,6 +2346,11 @@
           <t>Yevheniia Vlasenko</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1933,6 +2368,11 @@
           <t>Sofia Yurkiv</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1950,6 +2390,11 @@
           <t>Ivan Bekh</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1967,6 +2412,11 @@
           <t>Nazar-Marian Bakai</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1984,6 +2434,11 @@
           <t>Davyd Rozhkov</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2001,6 +2456,11 @@
           <t>Viktoriia Mysko</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2018,6 +2478,11 @@
           <t>Nazar Soloha</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2035,6 +2500,11 @@
           <t>Danil Diachenko</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2052,6 +2522,11 @@
           <t>Ihor Bohdan</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2069,6 +2544,11 @@
           <t>Mykhailo Shcherbyna</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2086,6 +2566,11 @@
           <t>Anastasiia Vynnyk</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2103,6 +2588,11 @@
           <t>Asan Khalilov</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2120,6 +2610,11 @@
           <t>Tetiana Krat</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2137,6 +2632,11 @@
           <t>Marharyta Kohut</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2154,6 +2654,11 @@
           <t>Yana Kovalenko</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2171,6 +2676,11 @@
           <t>Yelyzaveta Nadieieva</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2188,6 +2698,11 @@
           <t>Maksym Patrai</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2205,6 +2720,11 @@
           <t>Khrystyna Pelyno</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2222,6 +2742,11 @@
           <t>Mariia Tarasiuk</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2239,6 +2764,11 @@
           <t>Valentyna Vanzuriak</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2256,6 +2786,11 @@
           <t>Khrystyna Koprovska</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2273,6 +2808,11 @@
           <t>Yevhen Kushnyrik</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2290,6 +2830,11 @@
           <t>Maksym Kukharyk</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2307,6 +2852,11 @@
           <t>Danylo Hushcha</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2324,6 +2874,11 @@
           <t>Karolina Onyshchenko</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2341,6 +2896,11 @@
           <t>Yurii Sosnovskyi</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2358,6 +2918,11 @@
           <t>Vladyslav Tiutiunnyk</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2375,6 +2940,11 @@
           <t>Danyil Muravlov</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2392,6 +2962,11 @@
           <t>Anna Korkeshko</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2409,6 +2984,11 @@
           <t>Andriana Budysh</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2426,6 +3006,11 @@
           <t>Widgen Ropafadzo Tsabora</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2443,6 +3028,11 @@
           <t>Kamilla Kukri</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2460,6 +3050,11 @@
           <t>Sviatoslav Mezhivnyk</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2477,6 +3072,11 @@
           <t>Daryna Stankevych</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2494,6 +3094,11 @@
           <t>Marta Smuk</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2511,6 +3116,11 @@
           <t>Volodymyr Koziupa</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2528,6 +3138,11 @@
           <t>Oleksii Petrov</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2545,6 +3160,11 @@
           <t>Mariia Popova</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2562,6 +3182,11 @@
           <t>Yevheniia Prokopiv</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2579,6 +3204,11 @@
           <t>Valentyna Bulik</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2596,6 +3226,11 @@
           <t>Oksana Nykoliak</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2613,6 +3248,11 @@
           <t>Olena Dymura</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2630,6 +3270,11 @@
           <t>Yevheniia Vakulina</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2647,6 +3292,11 @@
           <t>Kateryna Dzyha</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2664,6 +3314,11 @@
           <t>Roman Sivak</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2681,6 +3336,11 @@
           <t>Orest Labiak</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2698,6 +3358,11 @@
           <t>Kostiantyn Pinchuk</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2715,6 +3380,11 @@
           <t>Anna Pozniak</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2732,6 +3402,11 @@
           <t>Anna Shumyk</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2749,6 +3424,11 @@
           <t>Anastasiia Lavryk</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2766,6 +3446,11 @@
           <t>Bogdan Ryabenko</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2783,6 +3468,11 @@
           <t>Vladyslava Zharska</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2800,6 +3490,11 @@
           <t>Dmytro Tkachenko</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2817,6 +3512,11 @@
           <t>Yelyzaveta Bozhko</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2834,6 +3534,11 @@
           <t>Olha Yaroshenko</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2851,6 +3556,11 @@
           <t>Kostiantyn Pohrebniak</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2868,6 +3578,11 @@
           <t>Denys Lebeda</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2885,6 +3600,11 @@
           <t>Yuliia Zhygulina</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2902,6 +3622,11 @@
           <t>Diana Rudzik</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2919,6 +3644,11 @@
           <t>Yakiv Kysliakov</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2936,6 +3666,11 @@
           <t>Nazar Drahomirov</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2953,6 +3688,11 @@
           <t>Volodymyr Larin</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2970,6 +3710,11 @@
           <t>Mariia Boncheva</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -2987,6 +3732,11 @@
           <t>Maksym Orlov1</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3004,6 +3754,11 @@
           <t>Mykhailo Senychych</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3021,6 +3776,11 @@
           <t>Yevhen Kelembet</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3038,6 +3798,11 @@
           <t>Volodymyr Larin</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3055,6 +3820,11 @@
           <t>Ihor Klimenchenko</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3072,6 +3842,11 @@
           <t>Maryna Polishchuk</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3089,6 +3864,11 @@
           <t>Anastasiia Kozbur</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3106,6 +3886,11 @@
           <t>Oleksandr Mykolaiko</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3123,6 +3908,11 @@
           <t>Valeriia Makovetska</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3140,6 +3930,11 @@
           <t>Olena Matviiv</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3157,6 +3952,11 @@
           <t>Maksym Kulish</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3174,6 +3974,11 @@
           <t>Victoria Kushnir</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3191,6 +3996,11 @@
           <t>Aleksandra Kvitka</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3208,6 +4018,11 @@
           <t>Mohamad Kawni</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3225,6 +4040,11 @@
           <t>Maryna Kibak</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3242,6 +4062,11 @@
           <t>Victoria Petrova</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3259,6 +4084,11 @@
           <t>Mykhailo Zelenchuk</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3276,6 +4106,11 @@
           <t>Mariia Shapovalenko</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3293,6 +4128,11 @@
           <t>Vladyslav Hoza</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3310,6 +4150,11 @@
           <t>Markiian Hanushevskyi</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3327,6 +4172,11 @@
           <t>Artem Sehal</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3344,6 +4194,11 @@
           <t>Ilona Ilieva</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3361,6 +4216,11 @@
           <t>Makar Bytsyura</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3378,6 +4238,11 @@
           <t>Taras Tiurdo</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3395,6 +4260,11 @@
           <t>Danylo Honchar</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3412,6 +4282,11 @@
           <t>Ivan Horobets</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3429,6 +4304,11 @@
           <t>Illia Yaremenko</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3446,6 +4326,11 @@
           <t>Anastasiia Ratushna</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3463,6 +4348,11 @@
           <t>Daniil Komiakov</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3480,6 +4370,11 @@
           <t>Denys Fedchenko</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3497,6 +4392,11 @@
           <t>Olesia Kuzyk</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3514,6 +4414,11 @@
           <t>Anastasiya Skibynska</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3531,6 +4436,11 @@
           <t>Ivan Kravchenko</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3548,6 +4458,11 @@
           <t>Valerii Zaiarnyi</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3565,6 +4480,11 @@
           <t>Viktoriia Avramenko</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3582,6 +4502,11 @@
           <t>Anhelina Turianska</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3599,6 +4524,11 @@
           <t>Olena Halaktionova</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3616,6 +4546,11 @@
           <t>Vitalii Radchenko</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3633,6 +4568,11 @@
           <t>Petro Fenenko</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3650,6 +4590,11 @@
           <t>Yevhen Fedorchenko</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3667,6 +4612,11 @@
           <t>Sofiia Zaianchkivska</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3684,6 +4634,11 @@
           <t>Oleksandr Matviichuk</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3701,6 +4656,11 @@
           <t>Valerii Toderiuk</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3718,6 +4678,11 @@
           <t>Mariana Humeniuk</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3735,6 +4700,11 @@
           <t>Viktor Lyulka</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3752,6 +4722,11 @@
           <t>Liudmyla Plekhanova</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3769,6 +4744,11 @@
           <t>Yehor Keller</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3786,6 +4766,11 @@
           <t>Dmytro Suprunets</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3803,6 +4788,11 @@
           <t>Viktor Dunets</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3820,6 +4810,11 @@
           <t>Nikita Havryliuk</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -3837,6 +4832,11 @@
           <t>Yuliia Bosko</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3854,6 +4854,11 @@
           <t>Alona Dehtiar</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3871,6 +4876,11 @@
           <t>Alina Nikolaieva</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3888,6 +4898,11 @@
           <t>Anastasiia Zykova</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3905,6 +4920,11 @@
           <t>Maksym Olynets</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3922,6 +4942,11 @@
           <t>Oleksandr Prepiialo</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3939,6 +4964,11 @@
           <t>Vadym Kharchenko</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3956,6 +4986,11 @@
           <t>Nikol Benua Berko</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3973,6 +5008,11 @@
           <t>Dmytro Mitsiuk</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3990,6 +5030,11 @@
           <t>Eduard Nesterenko</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4007,6 +5052,11 @@
           <t>Mariia Bodak</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4024,6 +5074,11 @@
           <t>Vitalii Marchenko</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4041,6 +5096,11 @@
           <t>Kostiantyn Bratchenko</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4058,6 +5118,11 @@
           <t>Romana Hrynovets</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4075,6 +5140,11 @@
           <t>Olha Prymak</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4092,6 +5162,11 @@
           <t>Veronika Bondar</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4109,6 +5184,11 @@
           <t>Nika Karpinska</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4126,6 +5206,11 @@
           <t>Valeriia Sereda</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4143,6 +5228,11 @@
           <t>Taras Tatarskyi</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4160,6 +5250,11 @@
           <t>Danylo Zhurniev</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4177,6 +5272,11 @@
           <t>Sofiia Bilyk</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4194,6 +5294,11 @@
           <t>Yuliia Hlynska</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4211,6 +5316,11 @@
           <t>Roman Zavhorodnii</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4228,6 +5338,11 @@
           <t>Artem Stratonov</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4245,6 +5360,11 @@
           <t>Denys Pronkin</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -4262,6 +5382,11 @@
           <t>Valerii Pylypenko</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4279,6 +5404,11 @@
           <t>Kateryna Lohin</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4296,6 +5426,11 @@
           <t>Arsen Shkolnyi</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4313,6 +5448,11 @@
           <t>Melusi Karen Kombore</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4330,6 +5470,11 @@
           <t>Kateryna Vasylovych</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4347,6 +5492,11 @@
           <t>Lolita Liushyn</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4364,6 +5514,11 @@
           <t>Alyona Zalevska</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>Privacy and Legal</t>
@@ -4381,6 +5536,11 @@
           <t>Iryna Tsolta</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4398,6 +5558,11 @@
           <t>Mykyta Koval</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -4415,6 +5580,11 @@
           <t>Sofiia Komziuk</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4432,6 +5602,11 @@
           <t>Dmytro Chaievskyi</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4449,6 +5624,11 @@
           <t>Diana Rykhalska</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4466,6 +5646,11 @@
           <t>Oleh Metlenko</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4483,6 +5668,11 @@
           <t>Maksym Starominskyi</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -4498,6 +5688,11 @@
       <c r="B240" t="inlineStr">
         <is>
           <t>Denys Hohol</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>EN I</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Payments and Safety</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Payments and Safety &amp; DSA</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -454,19 +454,14 @@
           <t>Anastasiia Sakharuk</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -476,19 +471,14 @@
           <t>Snizhana Zayats</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -498,19 +488,14 @@
           <t>Kateryna Podoliaka</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -520,19 +505,14 @@
           <t>Serhii Lutsenko</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -542,19 +522,14 @@
           <t>Mykhailo Cherepania</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -564,19 +539,14 @@
           <t>Tetiana Herman</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -586,19 +556,14 @@
           <t>Illia Makhniuk</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -608,19 +573,14 @@
           <t>Solomiia Krykhivska</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -630,19 +590,14 @@
           <t>Anastasiia Zaika</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -652,19 +607,14 @@
           <t>Anastasiia Zahoruiko</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -674,19 +624,14 @@
           <t>Nataliia Vonitova</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -696,19 +641,14 @@
           <t>Sesedzai Mudzingwa</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -718,19 +658,14 @@
           <t>Diana Khodan</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -740,19 +675,14 @@
           <t>Ihor Danyliak</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -762,19 +692,14 @@
           <t>Ashley Murerwa</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -784,19 +709,14 @@
           <t>Oleksii Pavlov</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -806,19 +726,14 @@
           <t>Yuliia Kravchuk</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -828,19 +743,14 @@
           <t>Ester Kovach</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -850,19 +760,14 @@
           <t>Anzhelika Kungurova</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -872,19 +777,14 @@
           <t>Dmytro Starozhytnyk</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -894,19 +794,14 @@
           <t>Nellia Kosenko</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -916,19 +811,14 @@
           <t>Andrii Abramov</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -938,19 +828,14 @@
           <t>Dmytro Lytvynenko</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -960,19 +845,14 @@
           <t>Tetiana Boiko</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -982,19 +862,14 @@
           <t>Vladyslav Vedmid</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1004,19 +879,14 @@
           <t>Oleksii Komar</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1026,19 +896,14 @@
           <t>Khrystyna Vyshnivska</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1048,19 +913,14 @@
           <t>Anastasiia Solodka</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1070,19 +930,14 @@
           <t>Yelyzaveta Tsyplenko</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1092,19 +947,14 @@
           <t>Karina Pilipuitis</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1114,19 +964,14 @@
           <t>Mariia Oros</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1136,19 +981,14 @@
           <t>Oleksander Sviatchenko</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1158,19 +998,14 @@
           <t>Anzhela Kulakova</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1180,19 +1015,14 @@
           <t>Bohdana Bohonos</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1202,19 +1032,14 @@
           <t>Vladyslav Kosovskyi</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1224,19 +1049,14 @@
           <t>Vladyslav Melnyk</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1246,19 +1066,14 @@
           <t>Tetiana Nazarenko</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1268,19 +1083,14 @@
           <t>Andrii Pryimenko</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1290,19 +1100,14 @@
           <t>Tetiana Kushnir</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1312,19 +1117,14 @@
           <t>Sofiia Maletska</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1334,19 +1134,14 @@
           <t>Andrii Manuliak</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1356,19 +1151,14 @@
           <t>Nataliia Trymbaliuk</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1378,19 +1168,14 @@
           <t>Sofiia Yukhymchuk</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1400,19 +1185,14 @@
           <t>Ilona Havryliuk</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1422,19 +1202,14 @@
           <t>Mariana Yuryshynets</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1444,19 +1219,14 @@
           <t>Anton Dmytruk</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1466,19 +1236,14 @@
           <t>Oleksandra Horobets</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1488,19 +1253,14 @@
           <t>Oleksandr Feshchuk</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1510,19 +1270,14 @@
           <t>Vitalii Yuzvyn</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1532,19 +1287,14 @@
           <t>Vladyslav Koreniuk</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1554,19 +1304,14 @@
           <t>Karolina-Anna Sikomas</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1576,19 +1321,14 @@
           <t>Dmytro Skrypak</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1598,19 +1338,14 @@
           <t>Yuliia Matviienko</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1620,19 +1355,14 @@
           <t>Mykola Sakalosh</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1642,19 +1372,14 @@
           <t>Hryhorii Balychev</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -1664,19 +1389,14 @@
           <t>Bohdana Rudnevska</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1686,19 +1406,14 @@
           <t>Anastasiia Volkanova</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -1708,19 +1423,14 @@
           <t>Olha Zubrytska</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1440,14 @@
           <t>Yevheniia Antonova</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1752,19 +1457,14 @@
           <t>Yekateryna Potsiluiko</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1774,19 +1474,14 @@
           <t>Andrii Venhreniuk</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -1796,19 +1491,14 @@
           <t>Yuliia Ruban</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1818,19 +1508,14 @@
           <t>Niiara Abdurakhmanova</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1840,19 +1525,14 @@
           <t>Romanna Paniush</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -1862,19 +1542,14 @@
           <t>Borys Suiarko</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1884,19 +1559,14 @@
           <t>Bohdana Kosarchyn</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1906,19 +1576,14 @@
           <t>Kateryna Mazurenko</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1928,19 +1593,14 @@
           <t>Oladipo Rahmon Saliu</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -1950,19 +1610,14 @@
           <t>Samuel Nwoke</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1972,19 +1627,14 @@
           <t>Anton Li</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -1994,19 +1644,14 @@
           <t>Marina Pidkovenko</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2016,19 +1661,14 @@
           <t>Anton Dovhyi</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2038,19 +1678,14 @@
           <t>Vladyslav Melnychuk</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2060,19 +1695,14 @@
           <t>Olena Yaremenko1</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2082,19 +1712,14 @@
           <t>Sebastian Stroin</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2104,19 +1729,14 @@
           <t>Olena Sharlai</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2126,19 +1746,14 @@
           <t>Veronika Dzhaparidze</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2148,19 +1763,14 @@
           <t>Nataliia Karpiuk</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2170,19 +1780,14 @@
           <t>Sofia Hunka1</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2192,19 +1797,14 @@
           <t>Vadym Rakitin</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2214,19 +1814,14 @@
           <t>Serhii Koval</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -2236,19 +1831,14 @@
           <t>Hlib Devecha</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -2258,19 +1848,14 @@
           <t>Marta Chipko</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -2280,19 +1865,14 @@
           <t>Korneliia Lopit</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -2302,19 +1882,14 @@
           <t>Yuliia Udut</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2324,19 +1899,14 @@
           <t>Bohdan Dunaievskyi</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2346,19 +1916,14 @@
           <t>Yevheniia Vlasenko</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -2368,19 +1933,14 @@
           <t>Sofia Yurkiv</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2390,19 +1950,14 @@
           <t>Ivan Bekh</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2412,19 +1967,14 @@
           <t>Nazar-Marian Bakai</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2434,19 +1984,14 @@
           <t>Davyd Rozhkov</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2456,19 +2001,14 @@
           <t>Viktoriia Mysko</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2478,19 +2018,14 @@
           <t>Nazar Soloha</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2500,19 +2035,14 @@
           <t>Danil Diachenko</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2522,19 +2052,14 @@
           <t>Ihor Bohdan</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2544,19 +2069,14 @@
           <t>Mykhailo Shcherbyna</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2566,19 +2086,14 @@
           <t>Anastasiia Vynnyk</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2588,19 +2103,14 @@
           <t>Asan Khalilov</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2610,19 +2120,14 @@
           <t>Tetiana Krat</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2632,19 +2137,14 @@
           <t>Marharyta Kohut</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2654,19 +2154,14 @@
           <t>Yana Kovalenko</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2676,19 +2171,14 @@
           <t>Yelyzaveta Nadieieva</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2698,19 +2188,14 @@
           <t>Maksym Patrai</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2720,19 +2205,14 @@
           <t>Khrystyna Pelyno</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2742,19 +2222,14 @@
           <t>Mariia Tarasiuk</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2764,19 +2239,14 @@
           <t>Valentyna Vanzuriak</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -2786,19 +2256,14 @@
           <t>Khrystyna Koprovska</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2808,19 +2273,14 @@
           <t>Yevhen Kushnyrik</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2830,19 +2290,14 @@
           <t>Maksym Kukharyk</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2852,19 +2307,14 @@
           <t>Danylo Hushcha</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2874,19 +2324,14 @@
           <t>Karolina Onyshchenko</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2896,19 +2341,14 @@
           <t>Yurii Sosnovskyi</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2918,19 +2358,14 @@
           <t>Vladyslav Tiutiunnyk</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -2940,19 +2375,14 @@
           <t>Danyil Muravlov</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2962,19 +2392,14 @@
           <t>Anna Korkeshko</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -2984,19 +2409,14 @@
           <t>Andriana Budysh</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3006,19 +2426,14 @@
           <t>Widgen Ropafadzo Tsabora</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3028,19 +2443,14 @@
           <t>Kamilla Kukri</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3050,19 +2460,14 @@
           <t>Sviatoslav Mezhivnyk</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3072,19 +2477,14 @@
           <t>Daryna Stankevych</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -3094,19 +2494,14 @@
           <t>Marta Smuk</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3116,19 +2511,14 @@
           <t>Volodymyr Koziupa</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3138,19 +2528,14 @@
           <t>Oleksii Petrov</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3160,19 +2545,14 @@
           <t>Mariia Popova</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3182,19 +2562,14 @@
           <t>Yevheniia Prokopiv</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3204,19 +2579,14 @@
           <t>Valentyna Bulik</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3226,19 +2596,14 @@
           <t>Oksana Nykoliak</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3248,19 +2613,14 @@
           <t>Olena Dymura</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3270,19 +2630,14 @@
           <t>Yevheniia Vakulina</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3292,19 +2647,14 @@
           <t>Kateryna Dzyha</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3314,19 +2664,14 @@
           <t>Roman Sivak</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3336,19 +2681,14 @@
           <t>Orest Labiak</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3358,19 +2698,14 @@
           <t>Kostiantyn Pinchuk</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3380,19 +2715,14 @@
           <t>Anna Pozniak</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3402,19 +2732,14 @@
           <t>Anna Shumyk</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3424,19 +2749,14 @@
           <t>Anastasiia Lavryk</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3446,19 +2766,14 @@
           <t>Bogdan Ryabenko</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3468,19 +2783,14 @@
           <t>Vladyslava Zharska</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3490,19 +2800,14 @@
           <t>Dmytro Tkachenko</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3512,19 +2817,14 @@
           <t>Yelyzaveta Bozhko</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3534,19 +2834,14 @@
           <t>Olha Yaroshenko</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3556,19 +2851,14 @@
           <t>Kostiantyn Pohrebniak</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -3578,19 +2868,14 @@
           <t>Denys Lebeda</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -3600,19 +2885,14 @@
           <t>Yuliia Zhygulina</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3622,19 +2902,14 @@
           <t>Diana Rudzik</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3644,19 +2919,14 @@
           <t>Yakiv Kysliakov</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3666,19 +2936,14 @@
           <t>Nazar Drahomirov</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -3688,19 +2953,14 @@
           <t>Volodymyr Larin</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3710,19 +2970,14 @@
           <t>Mariia Boncheva</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3732,19 +2987,14 @@
           <t>Maksym Orlov1</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3754,19 +3004,14 @@
           <t>Mykhailo Senychych</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3776,19 +3021,14 @@
           <t>Yevhen Kelembet</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -3798,19 +3038,14 @@
           <t>Volodymyr Larin</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -3820,19 +3055,14 @@
           <t>Ihor Klimenchenko</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3842,19 +3072,14 @@
           <t>Maryna Polishchuk</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3089,14 @@
           <t>Anastasiia Kozbur</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3886,19 +3106,14 @@
           <t>Oleksandr Mykolaiko</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3908,19 +3123,14 @@
           <t>Valeriia Makovetska</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3930,19 +3140,14 @@
           <t>Olena Matviiv</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3952,19 +3157,14 @@
           <t>Maksym Kulish</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3974,19 +3174,14 @@
           <t>Victoria Kushnir</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -3996,19 +3191,14 @@
           <t>Aleksandra Kvitka</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -4018,19 +3208,14 @@
           <t>Mohamad Kawni</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4040,19 +3225,14 @@
           <t>Maryna Kibak</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4062,19 +3242,14 @@
           <t>Victoria Petrova</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4084,19 +3259,14 @@
           <t>Mykhailo Zelenchuk</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4106,19 +3276,14 @@
           <t>Mariia Shapovalenko</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4128,19 +3293,14 @@
           <t>Vladyslav Hoza</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -4150,19 +3310,14 @@
           <t>Markiian Hanushevskyi</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4172,19 +3327,14 @@
           <t>Artem Sehal</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4194,19 +3344,14 @@
           <t>Ilona Ilieva</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4216,19 +3361,14 @@
           <t>Makar Bytsyura</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4238,19 +3378,14 @@
           <t>Taras Tiurdo</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4260,19 +3395,14 @@
           <t>Danylo Honchar</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4282,19 +3412,14 @@
           <t>Ivan Horobets</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4304,19 +3429,14 @@
           <t>Illia Yaremenko</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4326,19 +3446,14 @@
           <t>Anastasiia Ratushna</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4348,19 +3463,14 @@
           <t>Daniil Komiakov</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4370,19 +3480,14 @@
           <t>Denys Fedchenko</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4392,19 +3497,14 @@
           <t>Olesia Kuzyk</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4414,19 +3514,14 @@
           <t>Anastasiya Skibynska</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4436,19 +3531,14 @@
           <t>Ivan Kravchenko</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4458,19 +3548,14 @@
           <t>Valerii Zaiarnyi</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4480,19 +3565,14 @@
           <t>Viktoriia Avramenko</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4502,19 +3582,14 @@
           <t>Anhelina Turianska</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4524,19 +3599,14 @@
           <t>Olena Halaktionova</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4546,19 +3616,14 @@
           <t>Vitalii Radchenko</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4568,19 +3633,14 @@
           <t>Petro Fenenko</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4590,19 +3650,14 @@
           <t>Yevhen Fedorchenko</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4612,19 +3667,14 @@
           <t>Sofiia Zaianchkivska</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4634,19 +3684,14 @@
           <t>Oleksandr Matviichuk</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4656,19 +3701,14 @@
           <t>Valerii Toderiuk</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4678,19 +3718,14 @@
           <t>Mariana Humeniuk</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4700,19 +3735,14 @@
           <t>Viktor Lyulka</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4722,19 +3752,14 @@
           <t>Liudmyla Plekhanova</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4744,19 +3769,14 @@
           <t>Yehor Keller</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -4766,19 +3786,14 @@
           <t>Dmytro Suprunets</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4788,19 +3803,14 @@
           <t>Viktor Dunets</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4810,19 +3820,14 @@
           <t>Nikita Havryliuk</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -4832,19 +3837,14 @@
           <t>Yuliia Bosko</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4854,19 +3854,14 @@
           <t>Alona Dehtiar</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4876,19 +3871,14 @@
           <t>Alina Nikolaieva</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4898,19 +3888,14 @@
           <t>Anastasiia Zykova</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4920,19 +3905,14 @@
           <t>Maksym Olynets</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4942,19 +3922,14 @@
           <t>Oleksandr Prepiialo</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4964,19 +3939,14 @@
           <t>Vadym Kharchenko</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -4986,19 +3956,14 @@
           <t>Nikol Benua Berko</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5008,19 +3973,14 @@
           <t>Dmytro Mitsiuk</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5030,19 +3990,14 @@
           <t>Eduard Nesterenko</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5052,19 +4007,14 @@
           <t>Mariia Bodak</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5074,19 +4024,14 @@
           <t>Vitalii Marchenko</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5096,19 +4041,14 @@
           <t>Kostiantyn Bratchenko</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5118,19 +4058,14 @@
           <t>Romana Hrynovets</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -5140,19 +4075,14 @@
           <t>Olha Prymak</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5162,19 +4092,14 @@
           <t>Veronika Bondar</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5184,19 +4109,14 @@
           <t>Nika Karpinska</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5206,19 +4126,14 @@
           <t>Valeriia Sereda</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5228,19 +4143,14 @@
           <t>Taras Tatarskyi</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -5250,19 +4160,14 @@
           <t>Danylo Zhurniev</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5272,19 +4177,14 @@
           <t>Sofiia Bilyk</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5294,19 +4194,14 @@
           <t>Yuliia Hlynska</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -5316,19 +4211,14 @@
           <t>Roman Zavhorodnii</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5338,19 +4228,14 @@
           <t>Artem Stratonov</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5360,19 +4245,14 @@
           <t>Denys Pronkin</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5382,19 +4262,14 @@
           <t>Valerii Pylypenko</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5404,19 +4279,14 @@
           <t>Kateryna Lohin</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5426,19 +4296,14 @@
           <t>Arsen Shkolnyi</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5448,19 +4313,14 @@
           <t>Melusi Karen Kombore</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5470,19 +4330,14 @@
           <t>Kateryna Vasylovych</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -5492,19 +4347,14 @@
           <t>Lolita Liushyn</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
     </row>
@@ -5514,19 +4364,14 @@
           <t>Alyona Zalevska</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy &amp; Legal</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>DSA</t>
         </is>
       </c>
     </row>
@@ -5536,19 +4381,14 @@
           <t>Iryna Tsolta</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5558,19 +4398,14 @@
           <t>Mykyta Koval</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5580,19 +4415,14 @@
           <t>Sofiia Komziuk</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5602,19 +4432,14 @@
           <t>Dmytro Chaievskyi</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5624,19 +4449,14 @@
           <t>Diana Rykhalska</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>
@@ -5646,19 +4466,14 @@
           <t>Oleh Metlenko</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5668,19 +4483,14 @@
           <t>Maksym Starominskyi</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Payments and Safety &amp; DSA</t>
+          <t>Payments &amp; Safety</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5690,19 +4500,14 @@
           <t>Denys Hohol</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>EN I</t>
-        </is>
-      </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Shipping and Delivery</t>
+          <t>Shipping &amp; Delivery</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Order Quality and Usability</t>
+          <t>Order Quality &amp; Usability</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3040,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4162,12 +4162,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4213,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4315,12 +4315,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Privacy and Legal</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Privacy and Legal &amp; DSA</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/sample-data/desk_assignments.xlsx
+++ b/src/main/resources/sample-data/desk_assignments.xlsx
@@ -454,6 +454,11 @@
           <t>Anastasiia Sakharuk</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -471,6 +476,11 @@
           <t>Snizhana Zayats</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -488,6 +498,11 @@
           <t>Kateryna Podoliaka</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -505,6 +520,11 @@
           <t>Serhii Lutsenko</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -522,6 +542,11 @@
           <t>Mykhailo Cherepania</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -539,6 +564,11 @@
           <t>Tetiana Herman</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -556,6 +586,11 @@
           <t>Illia Makhniuk</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -573,6 +608,11 @@
           <t>Solomiia Krykhivska</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -590,6 +630,11 @@
           <t>Anastasiia Zaika</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -607,6 +652,11 @@
           <t>Anastasiia Zahoruiko</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -624,6 +674,11 @@
           <t>Nataliia Vonitova</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -641,6 +696,11 @@
           <t>Sesedzai Mudzingwa</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -658,6 +718,11 @@
           <t>Diana Khodan</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -675,6 +740,11 @@
           <t>Ihor Danyliak</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -692,6 +762,11 @@
           <t>Ashley Murerwa</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -709,6 +784,11 @@
           <t>Oleksii Pavlov</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -726,6 +806,11 @@
           <t>Yuliia Kravchuk</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -743,6 +828,11 @@
           <t>Ester Kovach</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -760,6 +850,11 @@
           <t>Anzhelika Kungurova</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -777,6 +872,11 @@
           <t>Dmytro Starozhytnyk</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -794,6 +894,11 @@
           <t>Nellia Kosenko</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -811,6 +916,11 @@
           <t>Andrii Abramov</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -828,6 +938,11 @@
           <t>Dmytro Lytvynenko</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -845,6 +960,11 @@
           <t>Tetiana Boiko</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -862,6 +982,11 @@
           <t>Vladyslav Vedmid</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -879,6 +1004,11 @@
           <t>Oleksii Komar</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -896,6 +1026,11 @@
           <t>Khrystyna Vyshnivska</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -913,6 +1048,11 @@
           <t>Anastasiia Solodka</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -930,6 +1070,11 @@
           <t>Yelyzaveta Tsyplenko</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -947,6 +1092,11 @@
           <t>Karina Pilipuitis</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -964,6 +1114,11 @@
           <t>Mariia Oros</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -981,6 +1136,11 @@
           <t>Oleksander Sviatchenko</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -998,6 +1158,11 @@
           <t>Anzhela Kulakova</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1015,6 +1180,11 @@
           <t>Bohdana Bohonos</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1032,6 +1202,11 @@
           <t>Vladyslav Kosovskyi</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1049,6 +1224,11 @@
           <t>Vladyslav Melnyk</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1066,6 +1246,11 @@
           <t>Tetiana Nazarenko</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1083,6 +1268,11 @@
           <t>Andrii Pryimenko</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1100,6 +1290,11 @@
           <t>Tetiana Kushnir</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1117,6 +1312,11 @@
           <t>Sofiia Maletska</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1134,6 +1334,11 @@
           <t>Andrii Manuliak</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1151,6 +1356,11 @@
           <t>Nataliia Trymbaliuk</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1168,6 +1378,11 @@
           <t>Sofiia Yukhymchuk</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1185,6 +1400,11 @@
           <t>Ilona Havryliuk</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1202,6 +1422,11 @@
           <t>Mariana Yuryshynets</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1219,6 +1444,11 @@
           <t>Anton Dmytruk</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1236,6 +1466,11 @@
           <t>Oleksandra Horobets</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1253,6 +1488,11 @@
           <t>Oleksandr Feshchuk</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1270,6 +1510,11 @@
           <t>Vitalii Yuzvyn</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1287,6 +1532,11 @@
           <t>Vladyslav Koreniuk</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1304,6 +1554,11 @@
           <t>Karolina-Anna Sikomas</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1321,6 +1576,11 @@
           <t>Dmytro Skrypak</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1338,6 +1598,11 @@
           <t>Yuliia Matviienko</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1355,6 +1620,11 @@
           <t>Mykola Sakalosh</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1372,6 +1642,11 @@
           <t>Hryhorii Balychev</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1389,6 +1664,11 @@
           <t>Bohdana Rudnevska</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1406,6 +1686,11 @@
           <t>Anastasiia Volkanova</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1423,6 +1708,11 @@
           <t>Olha Zubrytska</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1440,6 +1730,11 @@
           <t>Yevheniia Antonova</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1457,6 +1752,11 @@
           <t>Yekateryna Potsiluiko</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1474,6 +1774,11 @@
           <t>Andrii Venhreniuk</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -1491,6 +1796,11 @@
           <t>Yuliia Ruban</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1508,6 +1818,11 @@
           <t>Niiara Abdurakhmanova</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -1525,6 +1840,11 @@
           <t>Romanna Paniush</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -1542,6 +1862,11 @@
           <t>Borys Suiarko</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1559,6 +1884,11 @@
           <t>Bohdana Kosarchyn</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1576,6 +1906,11 @@
           <t>Kateryna Mazurenko</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1593,6 +1928,11 @@
           <t>Oladipo Rahmon Saliu</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1610,6 +1950,11 @@
           <t>Samuel Nwoke</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1627,6 +1972,11 @@
           <t>Anton Li</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1644,6 +1994,11 @@
           <t>Marina Pidkovenko</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1661,6 +2016,11 @@
           <t>Anton Dovhyi</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1678,6 +2038,11 @@
           <t>Vladyslav Melnychuk</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1695,6 +2060,11 @@
           <t>Olena Yaremenko1</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1712,6 +2082,11 @@
           <t>Sebastian Stroin</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1729,6 +2104,11 @@
           <t>Olena Sharlai</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1746,6 +2126,11 @@
           <t>Veronika Dzhaparidze</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1763,6 +2148,11 @@
           <t>Nataliia Karpiuk</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1780,6 +2170,11 @@
           <t>Sofia Hunka1</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1797,6 +2192,11 @@
           <t>Vadym Rakitin</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1814,6 +2214,11 @@
           <t>Serhii Koval</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1831,6 +2236,11 @@
           <t>Hlib Devecha</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1848,6 +2258,11 @@
           <t>Marta Chipko</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1865,6 +2280,11 @@
           <t>Korneliia Lopit</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1882,6 +2302,11 @@
           <t>Yuliia Udut</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1899,6 +2324,11 @@
           <t>Bohdan Dunaievskyi</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -1916,6 +2346,11 @@
           <t>Yevheniia Vlasenko</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1933,6 +2368,11 @@
           <t>Sofia Yurkiv</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -1950,6 +2390,11 @@
           <t>Ivan Bekh</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1967,6 +2412,11 @@
           <t>Nazar-Marian Bakai</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -1984,6 +2434,11 @@
           <t>Davyd Rozhkov</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2001,6 +2456,11 @@
           <t>Viktoriia Mysko</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2018,6 +2478,11 @@
           <t>Nazar Soloha</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2035,6 +2500,11 @@
           <t>Danil Diachenko</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2052,6 +2522,11 @@
           <t>Ihor Bohdan</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2069,6 +2544,11 @@
           <t>Mykhailo Shcherbyna</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2086,6 +2566,11 @@
           <t>Anastasiia Vynnyk</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2103,6 +2588,11 @@
           <t>Asan Khalilov</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2120,6 +2610,11 @@
           <t>Tetiana Krat</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2137,6 +2632,11 @@
           <t>Marharyta Kohut</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2154,6 +2654,11 @@
           <t>Yana Kovalenko</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2171,6 +2676,11 @@
           <t>Yelyzaveta Nadieieva</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2188,6 +2698,11 @@
           <t>Maksym Patrai</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2205,6 +2720,11 @@
           <t>Khrystyna Pelyno</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2222,6 +2742,11 @@
           <t>Mariia Tarasiuk</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2239,6 +2764,11 @@
           <t>Valentyna Vanzuriak</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2256,6 +2786,11 @@
           <t>Khrystyna Koprovska</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2273,6 +2808,11 @@
           <t>Yevhen Kushnyrik</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2290,6 +2830,11 @@
           <t>Maksym Kukharyk</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2307,6 +2852,11 @@
           <t>Danylo Hushcha</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2324,6 +2874,11 @@
           <t>Karolina Onyshchenko</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2341,6 +2896,11 @@
           <t>Yurii Sosnovskyi</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2358,6 +2918,11 @@
           <t>Vladyslav Tiutiunnyk</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2375,6 +2940,11 @@
           <t>Danyil Muravlov</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2392,6 +2962,11 @@
           <t>Anna Korkeshko</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2409,6 +2984,11 @@
           <t>Andriana Budysh</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2426,6 +3006,11 @@
           <t>Widgen Ropafadzo Tsabora</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2443,6 +3028,11 @@
           <t>Kamilla Kukri</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2460,6 +3050,11 @@
           <t>Sviatoslav Mezhivnyk</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2477,6 +3072,11 @@
           <t>Daryna Stankevych</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2494,6 +3094,11 @@
           <t>Marta Smuk</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2511,6 +3116,11 @@
           <t>Volodymyr Koziupa</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2528,6 +3138,11 @@
           <t>Oleksii Petrov</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2545,6 +3160,11 @@
           <t>Mariia Popova</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2562,6 +3182,11 @@
           <t>Yevheniia Prokopiv</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2579,6 +3204,11 @@
           <t>Valentyna Bulik</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2596,6 +3226,11 @@
           <t>Oksana Nykoliak</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2613,6 +3248,11 @@
           <t>Olena Dymura</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2630,6 +3270,11 @@
           <t>Yevheniia Vakulina</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2647,6 +3292,11 @@
           <t>Kateryna Dzyha</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2664,6 +3314,11 @@
           <t>Roman Sivak</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2681,6 +3336,11 @@
           <t>Orest Labiak</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2698,6 +3358,11 @@
           <t>Kostiantyn Pinchuk</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2715,6 +3380,11 @@
           <t>Anna Pozniak</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2732,6 +3402,11 @@
           <t>Anna Shumyk</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2749,6 +3424,11 @@
           <t>Anastasiia Lavryk</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2766,6 +3446,11 @@
           <t>Bogdan Ryabenko</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2783,6 +3468,11 @@
           <t>Vladyslava Zharska</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2800,6 +3490,11 @@
           <t>Dmytro Tkachenko</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2817,6 +3512,11 @@
           <t>Yelyzaveta Bozhko</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2834,6 +3534,11 @@
           <t>Olha Yaroshenko</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2851,6 +3556,11 @@
           <t>Kostiantyn Pohrebniak</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2868,6 +3578,11 @@
           <t>Denys Lebeda</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -2885,6 +3600,11 @@
           <t>Yuliia Zhygulina</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2902,6 +3622,11 @@
           <t>Diana Rudzik</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2919,6 +3644,11 @@
           <t>Yakiv Kysliakov</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -2936,6 +3666,11 @@
           <t>Nazar Drahomirov</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -2953,6 +3688,11 @@
           <t>Volodymyr Larin</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2970,6 +3710,11 @@
           <t>Mariia Boncheva</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -2987,6 +3732,11 @@
           <t>Maksym Orlov1</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3004,6 +3754,11 @@
           <t>Mykhailo Senychych</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3021,6 +3776,11 @@
           <t>Yevhen Kelembet</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3038,6 +3798,11 @@
           <t>Volodymyr Larin</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3055,6 +3820,11 @@
           <t>Ihor Klimenchenko</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3072,6 +3842,11 @@
           <t>Maryna Polishchuk</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3089,6 +3864,11 @@
           <t>Anastasiia Kozbur</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3106,6 +3886,11 @@
           <t>Oleksandr Mykolaiko</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3123,6 +3908,11 @@
           <t>Valeriia Makovetska</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3140,6 +3930,11 @@
           <t>Olena Matviiv</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3157,6 +3952,11 @@
           <t>Maksym Kulish</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3174,6 +3974,11 @@
           <t>Victoria Kushnir</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3191,6 +3996,11 @@
           <t>Aleksandra Kvitka</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3208,6 +4018,11 @@
           <t>Mohamad Kawni</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3225,6 +4040,11 @@
           <t>Maryna Kibak</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3242,6 +4062,11 @@
           <t>Victoria Petrova</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3259,6 +4084,11 @@
           <t>Mykhailo Zelenchuk</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3276,6 +4106,11 @@
           <t>Mariia Shapovalenko</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3293,6 +4128,11 @@
           <t>Vladyslav Hoza</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3310,6 +4150,11 @@
           <t>Markiian Hanushevskyi</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3327,6 +4172,11 @@
           <t>Artem Sehal</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3344,6 +4194,11 @@
           <t>Ilona Ilieva</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3361,6 +4216,11 @@
           <t>Makar Bytsyura</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3378,6 +4238,11 @@
           <t>Taras Tiurdo</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3395,6 +4260,11 @@
           <t>Danylo Honchar</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3412,6 +4282,11 @@
           <t>Ivan Horobets</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3429,6 +4304,11 @@
           <t>Illia Yaremenko</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3446,6 +4326,11 @@
           <t>Anastasiia Ratushna</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3463,6 +4348,11 @@
           <t>Daniil Komiakov</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3480,6 +4370,11 @@
           <t>Denys Fedchenko</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3497,6 +4392,11 @@
           <t>Olesia Kuzyk</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3514,6 +4414,11 @@
           <t>Anastasiya Skibynska</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3531,6 +4436,11 @@
           <t>Ivan Kravchenko</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3548,6 +4458,11 @@
           <t>Valerii Zaiarnyi</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3565,6 +4480,11 @@
           <t>Viktoriia Avramenko</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3582,6 +4502,11 @@
           <t>Anhelina Turianska</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3599,6 +4524,11 @@
           <t>Olena Halaktionova</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3616,6 +4546,11 @@
           <t>Vitalii Radchenko</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3633,6 +4568,11 @@
           <t>Petro Fenenko</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -3650,6 +4590,11 @@
           <t>Yevhen Fedorchenko</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3667,6 +4612,11 @@
           <t>Sofiia Zaianchkivska</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3684,6 +4634,11 @@
           <t>Oleksandr Matviichuk</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3701,6 +4656,11 @@
           <t>Valerii Toderiuk</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3718,6 +4678,11 @@
           <t>Mariana Humeniuk</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3735,6 +4700,11 @@
           <t>Viktor Lyulka</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3752,6 +4722,11 @@
           <t>Liudmyla Plekhanova</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3769,6 +4744,11 @@
           <t>Yehor Keller</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -3786,6 +4766,11 @@
           <t>Dmytro Suprunets</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3803,6 +4788,11 @@
           <t>Viktor Dunets</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3820,6 +4810,11 @@
           <t>Nikita Havryliuk</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -3837,6 +4832,11 @@
           <t>Yuliia Bosko</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3854,6 +4854,11 @@
           <t>Alona Dehtiar</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3871,6 +4876,11 @@
           <t>Alina Nikolaieva</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3888,6 +4898,11 @@
           <t>Anastasiia Zykova</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3905,6 +4920,11 @@
           <t>Maksym Olynets</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3922,6 +4942,11 @@
           <t>Oleksandr Prepiialo</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3939,6 +4964,11 @@
           <t>Vadym Kharchenko</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3956,6 +4986,11 @@
           <t>Nikol Benua Berko</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3973,6 +5008,11 @@
           <t>Dmytro Mitsiuk</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -3990,6 +5030,11 @@
           <t>Eduard Nesterenko</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4007,6 +5052,11 @@
           <t>Mariia Bodak</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4024,6 +5074,11 @@
           <t>Vitalii Marchenko</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4041,6 +5096,11 @@
           <t>Kostiantyn Bratchenko</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4058,6 +5118,11 @@
           <t>Romana Hrynovets</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4075,6 +5140,11 @@
           <t>Olha Prymak</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4092,6 +5162,11 @@
           <t>Veronika Bondar</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4109,6 +5184,11 @@
           <t>Nika Karpinska</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4126,6 +5206,11 @@
           <t>Valeriia Sereda</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4143,6 +5228,11 @@
           <t>Taras Tatarskyi</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4160,6 +5250,11 @@
           <t>Danylo Zhurniev</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4177,6 +5272,11 @@
           <t>Sofiia Bilyk</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4194,6 +5294,11 @@
           <t>Yuliia Hlynska</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4211,6 +5316,11 @@
           <t>Roman Zavhorodnii</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4228,6 +5338,11 @@
           <t>Artem Stratonov</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4245,6 +5360,11 @@
           <t>Denys Pronkin</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -4262,6 +5382,11 @@
           <t>Valerii Pylypenko</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4279,6 +5404,11 @@
           <t>Kateryna Lohin</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4296,6 +5426,11 @@
           <t>Arsen Shkolnyi</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4313,6 +5448,11 @@
           <t>Melusi Karen Kombore</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4330,6 +5470,11 @@
           <t>Kateryna Vasylovych</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4347,6 +5492,11 @@
           <t>Lolita Liushyn</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4364,6 +5514,11 @@
           <t>Alyona Zalevska</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>Privacy and Legal &amp; DSA</t>
@@ -4381,6 +5536,11 @@
           <t>Iryna Tsolta</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4398,6 +5558,11 @@
           <t>Mykyta Koval</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -4415,6 +5580,11 @@
           <t>Sofiia Komziuk</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4432,6 +5602,11 @@
           <t>Dmytro Chaievskyi</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4449,6 +5624,11 @@
           <t>Diana Rykhalska</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>Shipping and Delivery</t>
@@ -4466,6 +5646,11 @@
           <t>Oleh Metlenko</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>Order Quality and Usability</t>
@@ -4483,6 +5668,11 @@
           <t>Maksym Starominskyi</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>EN I</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>Payments and Safety</t>
@@ -4498,6 +5688,11 @@
       <c r="B240" t="inlineStr">
         <is>
           <t>Denys Hohol</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>EN I</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
